--- a/artfynd/A 46698-2021 artfynd.xlsx
+++ b/artfynd/A 46698-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46698-2021 artfynd.xlsx
+++ b/artfynd/A 46698-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101112117</v>
+        <v>101112263</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438340.2058109645</v>
+        <v>438437</v>
       </c>
       <c r="R2" t="n">
-        <v>6672031.123443216</v>
+        <v>6672080</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-05-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,54 +773,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101112248</v>
+        <v>104947196</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torrberget , Vrm</t>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438471.3863634269</v>
+        <v>438446</v>
       </c>
       <c r="R3" t="n">
-        <v>6671947.809178858</v>
+        <v>6672424</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,63 +858,58 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101112277</v>
+        <v>101112066</v>
       </c>
       <c r="B4" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Torrberget , Vrm</t>
+          <t>Torrberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438465.9242477139</v>
+        <v>438461</v>
       </c>
       <c r="R4" t="n">
-        <v>6672364.370907647</v>
+        <v>6672454</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +939,9 @@
           <t>2022-05-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +968,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101112263</v>
+        <v>104947261</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +979,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Torrberget , Vrm</t>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438437.7249969923</v>
+        <v>438290</v>
       </c>
       <c r="R5" t="n">
-        <v>6672080.237161008</v>
+        <v>6672082</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1033,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1049,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104947196</v>
+        <v>101112248</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1081,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+          <t>Torrberget , Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438446.4998012022</v>
+        <v>438471</v>
       </c>
       <c r="R6" t="n">
-        <v>6672424.402415623</v>
+        <v>6671948</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,22 +1136,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,27 +1156,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Stefan Holmqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Stefan Holmqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104947261</v>
+        <v>104947516</v>
       </c>
       <c r="B7" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438290.7259614334</v>
+        <v>438471</v>
       </c>
       <c r="R7" t="n">
-        <v>6672082.213192201</v>
+        <v>6671970</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,21 +1236,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1338,7 +1252,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverved av tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1356,37 +1270,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104947443</v>
+        <v>104947310</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438466.8570480579</v>
+        <v>438310</v>
       </c>
       <c r="R8" t="n">
-        <v>6672390.227560631</v>
+        <v>6672054</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,21 +1338,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1452,6 +1351,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>sälg/asp</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1471,12 +1375,7 @@
         <v>104947446</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438472.4984386302</v>
+        <v>438472</v>
       </c>
       <c r="R9" t="n">
-        <v>6672340.378150868</v>
+        <v>6672341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,19 +1440,9 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,37 +1474,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104947310</v>
+        <v>104947443</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1509,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438310.1793498538</v>
+        <v>438467</v>
       </c>
       <c r="R10" t="n">
-        <v>6672053.523019033</v>
+        <v>6672390</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,21 +1542,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1681,11 +1555,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>sälg/asp</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1702,15 +1571,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104947516</v>
+        <v>101112117</v>
       </c>
       <c r="B11" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,37 +1582,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+          <t>Torrberget , Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438470.7741645313</v>
+        <v>438340</v>
       </c>
       <c r="R11" t="n">
-        <v>6671970.709119887</v>
+        <v>6672031</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,22 +1637,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,24 +1653,117 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Stefan Holmqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Stefan Holmqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>101112277</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Torrberget , Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>438466</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6672365</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46698-2021 artfynd.xlsx
+++ b/artfynd/A 46698-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947196</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947261</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112248</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947516</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947310</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947446</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1568,6 +1613,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947443</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112117</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,8 +1819,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112277</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>